--- a/HNB/Areas/HnbBackoffice/HnbBackoffice_Postgre Specification.XLSX
+++ b/HNB/Areas/HnbBackoffice/HnbBackoffice_Postgre Specification.XLSX
@@ -1,20 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Ming\Private_project-GitHub-Horizon-Nova\Horizon_Nova\HNB\Areas\HnbBackoffice\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Private_project-GitHub-Horizon-Nova\Horizon_Nova\HNB\Areas\HnbBackoffice\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D44B69D3-F5A8-4D43-8E60-85F26D891FA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E2FD222-B931-494D-B461-DC24BEFD09A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12432" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Project" sheetId="19" r:id="rId1"/>
-    <sheet name="工作表1" sheetId="22" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -484,7 +483,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -526,15 +525,6 @@
       <name val="標楷體"/>
       <family val="4"/>
       <charset val="136"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="新細明體"/>
-      <family val="1"/>
-      <charset val="136"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="5">
@@ -601,7 +591,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -615,9 +605,6 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -629,9 +616,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -939,32 +923,32 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D5B9AB57-2E0C-49F5-AF44-C6B4EAB4221B}">
   <dimension ref="A1:K175"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.3" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
-    <col min="2" max="2" width="23.3984375" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.19921875" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="25.796875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="10.19921875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.41015625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.17578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="25.8203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="10.17578125" style="1" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="9" style="1" customWidth="1"/>
-    <col min="8" max="8" width="10.19921875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.5" style="1" customWidth="1"/>
-    <col min="10" max="10" width="33.296875" style="1" customWidth="1"/>
-    <col min="11" max="11" width="72.3984375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.17578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.46875" style="1" customWidth="1"/>
+    <col min="10" max="10" width="33.29296875" style="1" customWidth="1"/>
+    <col min="11" max="11" width="72.41015625" style="1" bestFit="1" customWidth="1"/>
     <col min="12" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="1" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="1" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="3" t="s">
         <v>0</v>
       </c>
@@ -999,1360 +983,1360 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A4" s="6">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4" s="5">
         <v>0</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="C4" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="D4" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="E4" s="6" t="s">
+      <c r="E4" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="F4" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="G4" s="6" t="s">
+      <c r="F4" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="G4" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="H4" s="6"/>
-      <c r="I4" s="6" t="s">
+      <c r="H4" s="5"/>
+      <c r="I4" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="J4" s="7"/>
-      <c r="K4" s="11">
+      <c r="J4" s="6"/>
+      <c r="K4" s="9">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A5" s="8">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5" s="7">
         <v>1</v>
       </c>
-      <c r="B5" s="8" t="s">
+      <c r="B5" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="C5" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="D5" s="8" t="s">
+      <c r="D5" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="E5" s="8" t="s">
+      <c r="E5" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="F5" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="G5" s="8" t="s">
+      <c r="F5" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="G5" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="H5" s="8"/>
-      <c r="I5" s="8" t="s">
+      <c r="H5" s="7"/>
+      <c r="I5" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="J5" s="9"/>
-      <c r="K5" s="9" t="s">
+      <c r="J5" s="8"/>
+      <c r="K5" s="8" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A6" s="6">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6" s="5">
         <v>2</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="C6" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="D6" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="E6" s="6" t="s">
+      <c r="E6" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="F6" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="G6" s="6" t="s">
+      <c r="F6" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="G6" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="H6" s="6"/>
-      <c r="I6" s="6" t="s">
+      <c r="H6" s="5"/>
+      <c r="I6" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="J6" s="7"/>
-      <c r="K6" s="11" t="s">
+      <c r="J6" s="6"/>
+      <c r="K6" s="9" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A7" s="8">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A7" s="7">
         <v>3</v>
       </c>
-      <c r="B7" s="8" t="s">
+      <c r="B7" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="C7" s="8" t="s">
+      <c r="C7" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="D7" s="8" t="s">
+      <c r="D7" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="E7" s="8" t="s">
+      <c r="E7" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="F7" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="G7" s="8" t="s">
+      <c r="F7" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="G7" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="H7" s="8"/>
-      <c r="I7" s="8" t="s">
+      <c r="H7" s="7"/>
+      <c r="I7" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="J7" s="9"/>
-      <c r="K7" s="9" t="s">
+      <c r="J7" s="8"/>
+      <c r="K7" s="8" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A8" s="6">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A8" s="5">
         <v>4</v>
       </c>
-      <c r="B8" s="6" t="s">
+      <c r="B8" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="C8" s="6" t="s">
+      <c r="C8" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="D8" s="6" t="s">
+      <c r="D8" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="E8" s="6" t="s">
+      <c r="E8" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="F8" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="G8" s="6" t="s">
+      <c r="F8" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="G8" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="H8" s="6"/>
-      <c r="I8" s="6" t="s">
+      <c r="H8" s="5"/>
+      <c r="I8" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="J8" s="7"/>
-      <c r="K8" s="11" t="s">
+      <c r="J8" s="6"/>
+      <c r="K8" s="9" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A9" s="8">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A9" s="7">
         <v>5</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="D9" s="8" t="s">
+      <c r="D9" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="E9" s="8" t="s">
+      <c r="E9" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="F9" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="G9" s="8" t="s">
+      <c r="F9" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="G9" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="H9" s="8"/>
-      <c r="I9" s="8" t="s">
+      <c r="H9" s="7"/>
+      <c r="I9" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="J9" s="9"/>
-      <c r="K9" s="9" t="b">
+      <c r="J9" s="8"/>
+      <c r="K9" s="8" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A10" s="6">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A10" s="5">
         <v>6</v>
       </c>
-      <c r="B10" s="6" t="s">
+      <c r="B10" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="C10" s="6" t="s">
+      <c r="C10" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="D10" s="6" t="s">
+      <c r="D10" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="E10" s="6" t="s">
+      <c r="E10" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="F10" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="G10" s="6" t="s">
+      <c r="F10" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="G10" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="H10" s="6"/>
-      <c r="I10" s="6" t="s">
+      <c r="H10" s="5"/>
+      <c r="I10" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="J10" s="7"/>
-      <c r="K10" s="11" t="b">
+      <c r="J10" s="6"/>
+      <c r="K10" s="9" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A11" s="8">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A11" s="7">
         <v>7</v>
       </c>
-      <c r="B11" s="8" t="s">
+      <c r="B11" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="C11" s="8" t="s">
+      <c r="C11" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="D11" s="8" t="s">
+      <c r="D11" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="E11" s="8" t="s">
+      <c r="E11" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="F11" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="G11" s="8" t="s">
+      <c r="F11" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="G11" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="H11" s="8"/>
-      <c r="I11" s="8" t="s">
+      <c r="H11" s="7"/>
+      <c r="I11" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="J11" s="9"/>
-      <c r="K11" s="9">
+      <c r="J11" s="8"/>
+      <c r="K11" s="8">
         <v>3600</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A12" s="6">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A12" s="5">
         <v>8</v>
       </c>
-      <c r="B12" s="6" t="s">
+      <c r="B12" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="C12" s="6" t="s">
+      <c r="C12" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="D12" s="6" t="s">
+      <c r="D12" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="E12" s="6" t="s">
+      <c r="E12" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="F12" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="G12" s="6" t="s">
+      <c r="F12" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="G12" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="H12" s="6"/>
-      <c r="I12" s="6" t="s">
+      <c r="H12" s="5"/>
+      <c r="I12" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="J12" s="7"/>
-      <c r="K12" s="11">
+      <c r="J12" s="6"/>
+      <c r="K12" s="9">
         <v>5</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A13" s="8">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A13" s="7">
         <v>9</v>
       </c>
-      <c r="B13" s="8" t="s">
+      <c r="B13" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="C13" s="8" t="s">
+      <c r="C13" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="D13" s="8" t="s">
+      <c r="D13" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="E13" s="8" t="s">
+      <c r="E13" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="F13" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="G13" s="8" t="s">
+      <c r="F13" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="G13" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="H13" s="8"/>
-      <c r="I13" s="8" t="s">
+      <c r="H13" s="7"/>
+      <c r="I13" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="J13" s="9"/>
-      <c r="K13" s="9" t="b">
+      <c r="J13" s="8"/>
+      <c r="K13" s="8" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A14" s="6">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A14" s="5">
         <v>10</v>
       </c>
-      <c r="B14" s="6" t="s">
+      <c r="B14" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="C14" s="6" t="s">
+      <c r="C14" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="D14" s="6" t="s">
+      <c r="D14" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="E14" s="6" t="s">
+      <c r="E14" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="F14" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="G14" s="6" t="s">
+      <c r="F14" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="G14" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="H14" s="6"/>
-      <c r="I14" s="6" t="s">
+      <c r="H14" s="5"/>
+      <c r="I14" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="J14" s="7"/>
-      <c r="K14" s="11" t="s">
+      <c r="J14" s="6"/>
+      <c r="K14" s="9" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A15" s="8">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A15" s="7">
         <v>11</v>
       </c>
-      <c r="B15" s="8" t="s">
+      <c r="B15" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="C15" s="8" t="s">
+      <c r="C15" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="D15" s="8" t="s">
+      <c r="D15" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="E15" s="8" t="s">
+      <c r="E15" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="F15" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="G15" s="8" t="s">
+      <c r="F15" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="G15" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="H15" s="8"/>
-      <c r="I15" s="8" t="s">
+      <c r="H15" s="7"/>
+      <c r="I15" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="J15" s="9"/>
-      <c r="K15" s="9" t="b">
+      <c r="J15" s="8"/>
+      <c r="K15" s="8" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A16" s="6">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A16" s="5">
         <v>12</v>
       </c>
-      <c r="B16" s="6" t="s">
+      <c r="B16" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="C16" s="6" t="s">
+      <c r="C16" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="D16" s="6" t="s">
+      <c r="D16" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="E16" s="6" t="s">
+      <c r="E16" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="F16" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="G16" s="6" t="s">
+      <c r="F16" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="G16" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="H16" s="6"/>
-      <c r="I16" s="6" t="s">
+      <c r="H16" s="5"/>
+      <c r="I16" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="J16" s="7"/>
-      <c r="K16" s="11" t="b">
+      <c r="J16" s="6"/>
+      <c r="K16" s="9" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A17" s="8">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A17" s="7">
         <v>13</v>
       </c>
-      <c r="B17" s="8" t="s">
+      <c r="B17" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="C17" s="8" t="s">
+      <c r="C17" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="D17" s="8" t="s">
+      <c r="D17" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="E17" s="8" t="s">
+      <c r="E17" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="F17" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="G17" s="8" t="s">
+      <c r="F17" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="G17" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="H17" s="8"/>
-      <c r="I17" s="8" t="s">
+      <c r="H17" s="7"/>
+      <c r="I17" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="J17" s="9"/>
-      <c r="K17" s="9" t="b">
+      <c r="J17" s="8"/>
+      <c r="K17" s="8" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A18" s="6">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A18" s="5">
         <v>14</v>
       </c>
-      <c r="B18" s="6" t="s">
+      <c r="B18" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="C18" s="6" t="s">
+      <c r="C18" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="D18" s="6" t="s">
+      <c r="D18" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="E18" s="6" t="s">
+      <c r="E18" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="F18" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="G18" s="6" t="s">
+      <c r="F18" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="G18" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="H18" s="6"/>
-      <c r="I18" s="6" t="s">
+      <c r="H18" s="5"/>
+      <c r="I18" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="J18" s="7"/>
-      <c r="K18" s="11" t="s">
+      <c r="J18" s="6"/>
+      <c r="K18" s="9" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A19" s="8">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A19" s="7">
         <v>15</v>
       </c>
-      <c r="B19" s="8" t="s">
+      <c r="B19" s="7" t="s">
         <v>90</v>
       </c>
-      <c r="C19" s="8" t="s">
+      <c r="C19" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="D19" s="8" t="s">
+      <c r="D19" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="E19" s="8" t="s">
+      <c r="E19" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="F19" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="G19" s="8" t="s">
+      <c r="F19" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="G19" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="H19" s="8"/>
-      <c r="I19" s="8" t="s">
+      <c r="H19" s="7"/>
+      <c r="I19" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="J19" s="9"/>
-      <c r="K19" s="9" t="s">
+      <c r="J19" s="8"/>
+      <c r="K19" s="8" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A20" s="6">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A20" s="5">
         <v>16</v>
       </c>
-      <c r="B20" s="6" t="s">
+      <c r="B20" s="5" t="s">
         <v>92</v>
       </c>
-      <c r="C20" s="6" t="s">
+      <c r="C20" s="5" t="s">
         <v>93</v>
       </c>
-      <c r="D20" s="6" t="s">
+      <c r="D20" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="E20" s="6" t="s">
+      <c r="E20" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="F20" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="G20" s="6" t="s">
+      <c r="F20" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="G20" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="H20" s="6"/>
-      <c r="I20" s="6" t="s">
+      <c r="H20" s="5"/>
+      <c r="I20" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="J20" s="7"/>
-      <c r="K20" s="11" t="s">
+      <c r="J20" s="6"/>
+      <c r="K20" s="9" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A21" s="8">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A21" s="7">
         <v>17</v>
       </c>
-      <c r="B21" s="8" t="s">
+      <c r="B21" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="C21" s="8" t="s">
+      <c r="C21" s="7" t="s">
         <v>95</v>
       </c>
-      <c r="D21" s="8" t="s">
+      <c r="D21" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="E21" s="8" t="s">
+      <c r="E21" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="F21" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="G21" s="8" t="s">
+      <c r="F21" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="G21" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="H21" s="8"/>
-      <c r="I21" s="8" t="s">
+      <c r="H21" s="7"/>
+      <c r="I21" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="J21" s="9"/>
-      <c r="K21" s="9">
+      <c r="J21" s="8"/>
+      <c r="K21" s="8">
         <v>3306</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A22" s="6">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A22" s="5">
         <v>18</v>
       </c>
-      <c r="B22" s="6" t="s">
+      <c r="B22" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="C22" s="6" t="s">
+      <c r="C22" s="5" t="s">
         <v>97</v>
       </c>
-      <c r="D22" s="6" t="s">
+      <c r="D22" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="E22" s="6" t="s">
+      <c r="E22" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="F22" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="G22" s="6" t="s">
+      <c r="F22" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="G22" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="H22" s="6"/>
-      <c r="I22" s="6" t="s">
+      <c r="H22" s="5"/>
+      <c r="I22" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="J22" s="7"/>
-      <c r="K22" s="11" t="s">
+      <c r="J22" s="6"/>
+      <c r="K22" s="9" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A23" s="8">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A23" s="7">
         <v>19</v>
       </c>
-      <c r="B23" s="8" t="s">
+      <c r="B23" s="7" t="s">
         <v>98</v>
       </c>
-      <c r="C23" s="8" t="s">
+      <c r="C23" s="7" t="s">
         <v>99</v>
       </c>
-      <c r="D23" s="8" t="s">
+      <c r="D23" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="E23" s="8" t="s">
+      <c r="E23" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="F23" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="G23" s="8" t="s">
+      <c r="F23" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="G23" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="H23" s="8"/>
-      <c r="I23" s="8" t="s">
+      <c r="H23" s="7"/>
+      <c r="I23" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="J23" s="9"/>
-      <c r="K23" s="9" t="s">
+      <c r="J23" s="8"/>
+      <c r="K23" s="8" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A24" s="6">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A24" s="5">
         <v>20</v>
       </c>
-      <c r="B24" s="6" t="s">
+      <c r="B24" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="C24" s="6" t="s">
+      <c r="C24" s="5" t="s">
         <v>101</v>
       </c>
-      <c r="D24" s="6" t="s">
+      <c r="D24" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="E24" s="6" t="s">
+      <c r="E24" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="F24" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="G24" s="6" t="s">
+      <c r="F24" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="G24" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="H24" s="6"/>
-      <c r="I24" s="6" t="s">
+      <c r="H24" s="5"/>
+      <c r="I24" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="J24" s="7"/>
-      <c r="K24" s="11" t="b">
+      <c r="J24" s="6"/>
+      <c r="K24" s="9" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A25" s="8">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A25" s="7">
         <v>21</v>
       </c>
-      <c r="B25" s="8" t="s">
+      <c r="B25" s="7" t="s">
         <v>102</v>
       </c>
-      <c r="C25" s="8" t="s">
+      <c r="C25" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="D25" s="8" t="s">
+      <c r="D25" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="E25" s="8" t="s">
+      <c r="E25" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="F25" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="G25" s="8" t="s">
+      <c r="F25" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="G25" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="H25" s="8"/>
-      <c r="I25" s="8" t="s">
+      <c r="H25" s="7"/>
+      <c r="I25" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="J25" s="9"/>
-      <c r="K25" s="9" t="s">
+      <c r="J25" s="8"/>
+      <c r="K25" s="8" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A26" s="6">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A26" s="5">
         <v>22</v>
       </c>
-      <c r="B26" s="6" t="s">
+      <c r="B26" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="C26" s="6" t="s">
+      <c r="C26" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="D26" s="6" t="s">
+      <c r="D26" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="E26" s="6" t="s">
+      <c r="E26" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="F26" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="G26" s="6" t="s">
+      <c r="F26" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="G26" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="H26" s="6"/>
-      <c r="I26" s="6" t="s">
+      <c r="H26" s="5"/>
+      <c r="I26" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="J26" s="7"/>
-      <c r="K26" s="11" t="s">
+      <c r="J26" s="6"/>
+      <c r="K26" s="9" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A27" s="8">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A27" s="7">
         <v>23</v>
       </c>
-      <c r="B27" s="8" t="s">
+      <c r="B27" s="7" t="s">
         <v>106</v>
       </c>
-      <c r="C27" s="8" t="s">
+      <c r="C27" s="7" t="s">
         <v>107</v>
       </c>
-      <c r="D27" s="8" t="s">
+      <c r="D27" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="E27" s="8" t="s">
+      <c r="E27" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="F27" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="G27" s="8" t="s">
+      <c r="F27" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="G27" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="H27" s="8"/>
-      <c r="I27" s="8" t="s">
+      <c r="H27" s="7"/>
+      <c r="I27" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="J27" s="9"/>
-      <c r="K27" s="9" t="s">
+      <c r="J27" s="8"/>
+      <c r="K27" s="8" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A28" s="6">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A28" s="5">
         <v>24</v>
       </c>
-      <c r="B28" s="6" t="s">
+      <c r="B28" s="5" t="s">
         <v>108</v>
       </c>
-      <c r="C28" s="6" t="s">
+      <c r="C28" s="5" t="s">
         <v>109</v>
       </c>
-      <c r="D28" s="6" t="s">
+      <c r="D28" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="E28" s="6" t="s">
+      <c r="E28" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="F28" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="G28" s="6" t="s">
+      <c r="F28" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="G28" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="H28" s="6"/>
-      <c r="I28" s="6" t="s">
+      <c r="H28" s="5"/>
+      <c r="I28" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="J28" s="7"/>
-      <c r="K28" s="11" t="s">
+      <c r="J28" s="6"/>
+      <c r="K28" s="9" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A29" s="8">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A29" s="7">
         <v>25</v>
       </c>
-      <c r="B29" s="8" t="s">
+      <c r="B29" s="7" t="s">
         <v>110</v>
       </c>
-      <c r="C29" s="8" t="s">
+      <c r="C29" s="7" t="s">
         <v>111</v>
       </c>
-      <c r="D29" s="8" t="s">
+      <c r="D29" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="E29" s="8" t="s">
+      <c r="E29" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="F29" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="G29" s="8" t="s">
+      <c r="F29" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="G29" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="H29" s="8"/>
-      <c r="I29" s="8" t="s">
+      <c r="H29" s="7"/>
+      <c r="I29" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="J29" s="8"/>
-      <c r="K29" s="9" t="s">
+      <c r="J29" s="7"/>
+      <c r="K29" s="8" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A30" s="6">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A30" s="5">
         <v>26</v>
       </c>
-      <c r="B30" s="6" t="s">
+      <c r="B30" s="5" t="s">
         <v>112</v>
       </c>
-      <c r="C30" s="6" t="s">
+      <c r="C30" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="D30" s="6" t="s">
+      <c r="D30" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="E30" s="6" t="s">
+      <c r="E30" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="F30" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="G30" s="6" t="s">
+      <c r="F30" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="G30" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="H30" s="6"/>
-      <c r="I30" s="6" t="s">
+      <c r="H30" s="5"/>
+      <c r="I30" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="J30" s="7"/>
-      <c r="K30" s="11" t="s">
+      <c r="J30" s="6"/>
+      <c r="K30" s="9" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A31" s="8">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A31" s="7">
         <v>27</v>
       </c>
-      <c r="B31" s="8" t="s">
+      <c r="B31" s="7" t="s">
         <v>114</v>
       </c>
-      <c r="C31" s="8" t="s">
+      <c r="C31" s="7" t="s">
         <v>115</v>
       </c>
-      <c r="D31" s="8" t="s">
+      <c r="D31" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="E31" s="8" t="s">
+      <c r="E31" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="F31" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="G31" s="8" t="s">
+      <c r="F31" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="G31" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="H31" s="8"/>
-      <c r="I31" s="8" t="s">
+      <c r="H31" s="7"/>
+      <c r="I31" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="J31" s="9"/>
-      <c r="K31" s="9" t="s">
+      <c r="J31" s="8"/>
+      <c r="K31" s="8" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A32" s="6">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A32" s="5">
         <v>28</v>
       </c>
-      <c r="B32" s="6" t="s">
+      <c r="B32" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="C32" s="6" t="s">
+      <c r="C32" s="5" t="s">
         <v>117</v>
       </c>
-      <c r="D32" s="6" t="s">
+      <c r="D32" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="E32" s="6" t="s">
+      <c r="E32" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="F32" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="G32" s="6" t="s">
+      <c r="F32" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="G32" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="H32" s="6"/>
-      <c r="I32" s="6" t="s">
+      <c r="H32" s="5"/>
+      <c r="I32" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="J32" s="7"/>
-      <c r="K32" s="11" t="s">
+      <c r="J32" s="6"/>
+      <c r="K32" s="9" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A33" s="8">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A33" s="7">
         <v>29</v>
       </c>
-      <c r="B33" s="8" t="s">
+      <c r="B33" s="7" t="s">
         <v>118</v>
       </c>
-      <c r="C33" s="8" t="s">
+      <c r="C33" s="7" t="s">
         <v>119</v>
       </c>
-      <c r="D33" s="8" t="s">
+      <c r="D33" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="E33" s="8" t="s">
+      <c r="E33" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="F33" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="G33" s="8" t="s">
+      <c r="F33" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="G33" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="H33" s="8"/>
-      <c r="I33" s="8" t="s">
+      <c r="H33" s="7"/>
+      <c r="I33" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="J33" s="9"/>
-      <c r="K33" s="9" t="s">
+      <c r="J33" s="8"/>
+      <c r="K33" s="8" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="D34" s="2"/>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="D35" s="2"/>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="D36" s="2"/>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="D37" s="2"/>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="D38" s="2"/>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="D39" s="2"/>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="D40" s="2"/>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="D41" s="2"/>
     </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="D42" s="2"/>
     </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="D43" s="2"/>
     </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="D44" s="2"/>
     </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="D45" s="2"/>
     </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="D46" s="2"/>
     </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="D47" s="2"/>
     </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="D48" s="2"/>
     </row>
-    <row r="49" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="49" spans="4:4" x14ac:dyDescent="0.55000000000000004">
       <c r="D49" s="2"/>
     </row>
-    <row r="50" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="50" spans="4:4" x14ac:dyDescent="0.55000000000000004">
       <c r="D50" s="2"/>
     </row>
-    <row r="51" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="51" spans="4:4" x14ac:dyDescent="0.55000000000000004">
       <c r="D51" s="2"/>
     </row>
-    <row r="52" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="52" spans="4:4" x14ac:dyDescent="0.55000000000000004">
       <c r="D52" s="2"/>
     </row>
-    <row r="53" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="53" spans="4:4" x14ac:dyDescent="0.55000000000000004">
       <c r="D53" s="2"/>
     </row>
-    <row r="54" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="54" spans="4:4" x14ac:dyDescent="0.55000000000000004">
       <c r="D54" s="2"/>
     </row>
-    <row r="55" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="55" spans="4:4" x14ac:dyDescent="0.55000000000000004">
       <c r="D55" s="2"/>
     </row>
-    <row r="56" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="56" spans="4:4" x14ac:dyDescent="0.55000000000000004">
       <c r="D56" s="2"/>
     </row>
-    <row r="57" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="57" spans="4:4" x14ac:dyDescent="0.55000000000000004">
       <c r="D57" s="2"/>
     </row>
-    <row r="58" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="58" spans="4:4" x14ac:dyDescent="0.55000000000000004">
       <c r="D58" s="2"/>
     </row>
-    <row r="59" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="59" spans="4:4" x14ac:dyDescent="0.55000000000000004">
       <c r="D59" s="2"/>
     </row>
-    <row r="60" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="60" spans="4:4" x14ac:dyDescent="0.55000000000000004">
       <c r="D60" s="2"/>
     </row>
-    <row r="61" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="61" spans="4:4" x14ac:dyDescent="0.55000000000000004">
       <c r="D61" s="2"/>
     </row>
-    <row r="62" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="62" spans="4:4" x14ac:dyDescent="0.55000000000000004">
       <c r="D62" s="2"/>
     </row>
-    <row r="63" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="63" spans="4:4" x14ac:dyDescent="0.55000000000000004">
       <c r="D63" s="2"/>
     </row>
-    <row r="64" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="64" spans="4:4" x14ac:dyDescent="0.55000000000000004">
       <c r="D64" s="2"/>
     </row>
-    <row r="65" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="65" spans="4:4" x14ac:dyDescent="0.55000000000000004">
       <c r="D65" s="2"/>
     </row>
-    <row r="66" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="66" spans="4:4" x14ac:dyDescent="0.55000000000000004">
       <c r="D66" s="2"/>
     </row>
-    <row r="67" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="67" spans="4:4" x14ac:dyDescent="0.55000000000000004">
       <c r="D67" s="2"/>
     </row>
-    <row r="68" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="68" spans="4:4" x14ac:dyDescent="0.55000000000000004">
       <c r="D68" s="2"/>
     </row>
-    <row r="69" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="69" spans="4:4" x14ac:dyDescent="0.55000000000000004">
       <c r="D69" s="2"/>
     </row>
-    <row r="70" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="70" spans="4:4" x14ac:dyDescent="0.55000000000000004">
       <c r="D70" s="2"/>
     </row>
-    <row r="71" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="71" spans="4:4" x14ac:dyDescent="0.55000000000000004">
       <c r="D71" s="2"/>
     </row>
-    <row r="72" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="72" spans="4:4" x14ac:dyDescent="0.55000000000000004">
       <c r="D72" s="2"/>
     </row>
-    <row r="73" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="73" spans="4:4" x14ac:dyDescent="0.55000000000000004">
       <c r="D73" s="2"/>
     </row>
-    <row r="74" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="74" spans="4:4" x14ac:dyDescent="0.55000000000000004">
       <c r="D74" s="2"/>
     </row>
-    <row r="75" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="75" spans="4:4" x14ac:dyDescent="0.55000000000000004">
       <c r="D75" s="2"/>
     </row>
-    <row r="76" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="76" spans="4:4" x14ac:dyDescent="0.55000000000000004">
       <c r="D76" s="2"/>
     </row>
-    <row r="77" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="77" spans="4:4" x14ac:dyDescent="0.55000000000000004">
       <c r="D77" s="2"/>
     </row>
-    <row r="78" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="78" spans="4:4" x14ac:dyDescent="0.55000000000000004">
       <c r="D78" s="2"/>
     </row>
-    <row r="79" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="79" spans="4:4" x14ac:dyDescent="0.55000000000000004">
       <c r="D79" s="2"/>
     </row>
-    <row r="80" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="80" spans="4:4" x14ac:dyDescent="0.55000000000000004">
       <c r="D80" s="2"/>
     </row>
-    <row r="81" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="81" spans="4:4" x14ac:dyDescent="0.55000000000000004">
       <c r="D81" s="2"/>
     </row>
-    <row r="82" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="82" spans="4:4" x14ac:dyDescent="0.55000000000000004">
       <c r="D82" s="2"/>
     </row>
-    <row r="83" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="83" spans="4:4" x14ac:dyDescent="0.55000000000000004">
       <c r="D83" s="2"/>
     </row>
-    <row r="84" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="84" spans="4:4" x14ac:dyDescent="0.55000000000000004">
       <c r="D84" s="2"/>
     </row>
-    <row r="85" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="85" spans="4:4" x14ac:dyDescent="0.55000000000000004">
       <c r="D85" s="2"/>
     </row>
-    <row r="86" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="86" spans="4:4" x14ac:dyDescent="0.55000000000000004">
       <c r="D86" s="2"/>
     </row>
-    <row r="87" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="87" spans="4:4" x14ac:dyDescent="0.55000000000000004">
       <c r="D87" s="2"/>
     </row>
-    <row r="88" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="88" spans="4:4" x14ac:dyDescent="0.55000000000000004">
       <c r="D88" s="2"/>
     </row>
-    <row r="89" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="89" spans="4:4" x14ac:dyDescent="0.55000000000000004">
       <c r="D89" s="2"/>
     </row>
-    <row r="90" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="90" spans="4:4" x14ac:dyDescent="0.55000000000000004">
       <c r="D90" s="2"/>
     </row>
-    <row r="91" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="91" spans="4:4" x14ac:dyDescent="0.55000000000000004">
       <c r="D91" s="2"/>
     </row>
-    <row r="92" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="92" spans="4:4" x14ac:dyDescent="0.55000000000000004">
       <c r="D92" s="2"/>
     </row>
-    <row r="93" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="93" spans="4:4" x14ac:dyDescent="0.55000000000000004">
       <c r="D93" s="2"/>
     </row>
-    <row r="94" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="94" spans="4:4" x14ac:dyDescent="0.55000000000000004">
       <c r="D94" s="2"/>
     </row>
-    <row r="95" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="95" spans="4:4" x14ac:dyDescent="0.55000000000000004">
       <c r="D95" s="2"/>
     </row>
-    <row r="96" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="96" spans="4:4" x14ac:dyDescent="0.55000000000000004">
       <c r="D96" s="2"/>
     </row>
-    <row r="97" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="97" spans="4:4" x14ac:dyDescent="0.55000000000000004">
       <c r="D97" s="2"/>
     </row>
-    <row r="98" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="98" spans="4:4" x14ac:dyDescent="0.55000000000000004">
       <c r="D98" s="2"/>
     </row>
-    <row r="99" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="99" spans="4:4" x14ac:dyDescent="0.55000000000000004">
       <c r="D99" s="2"/>
     </row>
-    <row r="100" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="100" spans="4:4" x14ac:dyDescent="0.55000000000000004">
       <c r="D100" s="2"/>
     </row>
-    <row r="101" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="101" spans="4:4" x14ac:dyDescent="0.55000000000000004">
       <c r="D101" s="2"/>
     </row>
-    <row r="102" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="102" spans="4:4" x14ac:dyDescent="0.55000000000000004">
       <c r="D102" s="2"/>
     </row>
-    <row r="103" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="103" spans="4:4" x14ac:dyDescent="0.55000000000000004">
       <c r="D103" s="2"/>
     </row>
-    <row r="104" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="104" spans="4:4" x14ac:dyDescent="0.55000000000000004">
       <c r="D104" s="2"/>
     </row>
-    <row r="105" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="105" spans="4:4" x14ac:dyDescent="0.55000000000000004">
       <c r="D105" s="2"/>
     </row>
-    <row r="106" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="106" spans="4:4" x14ac:dyDescent="0.55000000000000004">
       <c r="D106" s="2"/>
     </row>
-    <row r="107" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="107" spans="4:4" x14ac:dyDescent="0.55000000000000004">
       <c r="D107" s="2"/>
     </row>
-    <row r="108" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="108" spans="4:4" x14ac:dyDescent="0.55000000000000004">
       <c r="D108" s="2"/>
     </row>
-    <row r="109" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="109" spans="4:4" x14ac:dyDescent="0.55000000000000004">
       <c r="D109" s="2"/>
     </row>
-    <row r="110" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="110" spans="4:4" x14ac:dyDescent="0.55000000000000004">
       <c r="D110" s="2"/>
     </row>
-    <row r="111" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="111" spans="4:4" x14ac:dyDescent="0.55000000000000004">
       <c r="D111" s="2"/>
     </row>
-    <row r="112" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="112" spans="4:4" x14ac:dyDescent="0.55000000000000004">
       <c r="D112" s="2"/>
     </row>
-    <row r="113" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="113" spans="4:4" x14ac:dyDescent="0.55000000000000004">
       <c r="D113" s="2"/>
     </row>
-    <row r="114" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="114" spans="4:4" x14ac:dyDescent="0.55000000000000004">
       <c r="D114" s="2"/>
     </row>
-    <row r="115" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="115" spans="4:4" x14ac:dyDescent="0.55000000000000004">
       <c r="D115" s="2"/>
     </row>
-    <row r="116" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="116" spans="4:4" x14ac:dyDescent="0.55000000000000004">
       <c r="D116" s="2"/>
     </row>
-    <row r="117" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="117" spans="4:4" x14ac:dyDescent="0.55000000000000004">
       <c r="D117" s="2"/>
     </row>
-    <row r="118" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="118" spans="4:4" x14ac:dyDescent="0.55000000000000004">
       <c r="D118" s="2"/>
     </row>
-    <row r="119" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="119" spans="4:4" x14ac:dyDescent="0.55000000000000004">
       <c r="D119" s="2"/>
     </row>
-    <row r="120" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="120" spans="4:4" x14ac:dyDescent="0.55000000000000004">
       <c r="D120" s="2"/>
     </row>
-    <row r="121" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="121" spans="4:4" x14ac:dyDescent="0.55000000000000004">
       <c r="D121" s="2"/>
     </row>
-    <row r="122" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="122" spans="4:4" x14ac:dyDescent="0.55000000000000004">
       <c r="D122" s="2"/>
     </row>
-    <row r="123" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="123" spans="4:4" x14ac:dyDescent="0.55000000000000004">
       <c r="D123" s="2"/>
     </row>
-    <row r="124" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="124" spans="4:4" x14ac:dyDescent="0.55000000000000004">
       <c r="D124" s="2"/>
     </row>
-    <row r="125" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="125" spans="4:4" x14ac:dyDescent="0.55000000000000004">
       <c r="D125" s="2"/>
     </row>
-    <row r="126" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="126" spans="4:4" x14ac:dyDescent="0.55000000000000004">
       <c r="D126" s="2"/>
     </row>
-    <row r="127" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="127" spans="4:4" x14ac:dyDescent="0.55000000000000004">
       <c r="D127" s="2"/>
     </row>
-    <row r="128" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="128" spans="4:4" x14ac:dyDescent="0.55000000000000004">
       <c r="D128" s="2"/>
     </row>
-    <row r="129" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="129" spans="4:4" x14ac:dyDescent="0.55000000000000004">
       <c r="D129" s="2"/>
     </row>
-    <row r="130" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="130" spans="4:4" x14ac:dyDescent="0.55000000000000004">
       <c r="D130" s="2"/>
     </row>
-    <row r="131" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="131" spans="4:4" x14ac:dyDescent="0.55000000000000004">
       <c r="D131" s="2"/>
     </row>
-    <row r="132" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="132" spans="4:4" x14ac:dyDescent="0.55000000000000004">
       <c r="D132" s="2"/>
     </row>
-    <row r="133" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="133" spans="4:4" x14ac:dyDescent="0.55000000000000004">
       <c r="D133" s="2"/>
     </row>
-    <row r="134" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="134" spans="4:4" x14ac:dyDescent="0.55000000000000004">
       <c r="D134" s="2"/>
     </row>
-    <row r="135" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="135" spans="4:4" x14ac:dyDescent="0.55000000000000004">
       <c r="D135" s="2"/>
     </row>
-    <row r="136" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="136" spans="4:4" x14ac:dyDescent="0.55000000000000004">
       <c r="D136" s="2"/>
     </row>
-    <row r="137" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="137" spans="4:4" x14ac:dyDescent="0.55000000000000004">
       <c r="D137" s="2"/>
     </row>
-    <row r="138" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="138" spans="4:4" x14ac:dyDescent="0.55000000000000004">
       <c r="D138" s="2"/>
     </row>
-    <row r="139" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="139" spans="4:4" x14ac:dyDescent="0.55000000000000004">
       <c r="D139" s="2"/>
     </row>
-    <row r="140" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="140" spans="4:4" x14ac:dyDescent="0.55000000000000004">
       <c r="D140" s="2"/>
     </row>
-    <row r="141" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="141" spans="4:4" x14ac:dyDescent="0.55000000000000004">
       <c r="D141" s="2"/>
     </row>
-    <row r="142" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="142" spans="4:4" x14ac:dyDescent="0.55000000000000004">
       <c r="D142" s="2"/>
     </row>
-    <row r="143" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="143" spans="4:4" x14ac:dyDescent="0.55000000000000004">
       <c r="D143" s="2"/>
     </row>
-    <row r="144" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="144" spans="4:4" x14ac:dyDescent="0.55000000000000004">
       <c r="D144" s="2"/>
     </row>
-    <row r="145" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="145" spans="4:4" x14ac:dyDescent="0.55000000000000004">
       <c r="D145" s="2"/>
     </row>
-    <row r="146" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="146" spans="4:4" x14ac:dyDescent="0.55000000000000004">
       <c r="D146" s="2"/>
     </row>
-    <row r="147" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="147" spans="4:4" x14ac:dyDescent="0.55000000000000004">
       <c r="D147" s="2"/>
     </row>
-    <row r="148" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="148" spans="4:4" x14ac:dyDescent="0.55000000000000004">
       <c r="D148" s="2"/>
     </row>
-    <row r="149" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="149" spans="4:4" x14ac:dyDescent="0.55000000000000004">
       <c r="D149" s="2"/>
     </row>
-    <row r="150" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="150" spans="4:4" x14ac:dyDescent="0.55000000000000004">
       <c r="D150" s="2"/>
     </row>
-    <row r="151" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="151" spans="4:4" x14ac:dyDescent="0.55000000000000004">
       <c r="D151" s="2"/>
     </row>
-    <row r="152" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="152" spans="4:4" x14ac:dyDescent="0.55000000000000004">
       <c r="D152" s="2"/>
     </row>
-    <row r="153" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="153" spans="4:4" x14ac:dyDescent="0.55000000000000004">
       <c r="D153" s="2"/>
     </row>
-    <row r="154" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="154" spans="4:4" x14ac:dyDescent="0.55000000000000004">
       <c r="D154" s="2"/>
     </row>
-    <row r="155" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="155" spans="4:4" x14ac:dyDescent="0.55000000000000004">
       <c r="D155" s="2"/>
     </row>
-    <row r="156" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="156" spans="4:4" x14ac:dyDescent="0.55000000000000004">
       <c r="D156" s="2"/>
     </row>
-    <row r="157" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="157" spans="4:4" x14ac:dyDescent="0.55000000000000004">
       <c r="D157" s="2"/>
     </row>
-    <row r="158" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="158" spans="4:4" x14ac:dyDescent="0.55000000000000004">
       <c r="D158" s="2"/>
     </row>
-    <row r="159" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="159" spans="4:4" x14ac:dyDescent="0.55000000000000004">
       <c r="D159" s="2"/>
     </row>
-    <row r="160" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="160" spans="4:4" x14ac:dyDescent="0.55000000000000004">
       <c r="D160" s="2"/>
     </row>
-    <row r="161" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="161" spans="4:4" x14ac:dyDescent="0.55000000000000004">
       <c r="D161" s="2"/>
     </row>
-    <row r="162" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="162" spans="4:4" x14ac:dyDescent="0.55000000000000004">
       <c r="D162" s="2"/>
     </row>
-    <row r="163" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="163" spans="4:4" x14ac:dyDescent="0.55000000000000004">
       <c r="D163" s="2"/>
     </row>
-    <row r="164" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="164" spans="4:4" x14ac:dyDescent="0.55000000000000004">
       <c r="D164" s="2"/>
     </row>
-    <row r="165" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="165" spans="4:4" x14ac:dyDescent="0.55000000000000004">
       <c r="D165" s="2"/>
     </row>
-    <row r="166" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="166" spans="4:4" x14ac:dyDescent="0.55000000000000004">
       <c r="D166" s="2"/>
     </row>
-    <row r="167" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="167" spans="4:4" x14ac:dyDescent="0.55000000000000004">
       <c r="D167" s="2"/>
     </row>
-    <row r="168" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="168" spans="4:4" x14ac:dyDescent="0.55000000000000004">
       <c r="D168" s="2"/>
     </row>
-    <row r="169" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="169" spans="4:4" x14ac:dyDescent="0.55000000000000004">
       <c r="D169" s="2"/>
     </row>
-    <row r="170" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="170" spans="4:4" x14ac:dyDescent="0.55000000000000004">
       <c r="D170" s="2"/>
     </row>
-    <row r="171" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="171" spans="4:4" x14ac:dyDescent="0.55000000000000004">
       <c r="D171" s="2"/>
     </row>
-    <row r="172" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="172" spans="4:4" x14ac:dyDescent="0.55000000000000004">
       <c r="D172" s="2"/>
     </row>
-    <row r="173" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="173" spans="4:4" x14ac:dyDescent="0.55000000000000004">
       <c r="D173" s="2"/>
     </row>
-    <row r="174" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="174" spans="4:4" x14ac:dyDescent="0.55000000000000004">
       <c r="D174" s="2"/>
     </row>
-    <row r="175" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="175" spans="4:4" x14ac:dyDescent="0.55000000000000004">
       <c r="D175" s="2"/>
     </row>
   </sheetData>
@@ -2360,325 +2344,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{926EAD58-6292-4AA6-BAFB-982896E6AC80}">
-  <dimension ref="A1:H31"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.3"/>
-  <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1" s="10"/>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
-      <c r="F1" s="10"/>
-      <c r="G1" s="10"/>
-      <c r="H1" s="10"/>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A2" s="5"/>
-      <c r="B2" s="5"/>
-      <c r="C2" s="5"/>
-      <c r="D2" s="5"/>
-      <c r="E2" s="5"/>
-      <c r="F2" s="5"/>
-      <c r="G2" s="5"/>
-      <c r="H2" s="5"/>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A3" s="5"/>
-      <c r="B3" s="5"/>
-      <c r="C3" s="5"/>
-      <c r="D3" s="5"/>
-      <c r="E3" s="5"/>
-      <c r="F3" s="5"/>
-      <c r="G3" s="5"/>
-      <c r="H3" s="5"/>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A4" s="5"/>
-      <c r="B4" s="5"/>
-      <c r="C4" s="5"/>
-      <c r="D4" s="5"/>
-      <c r="E4" s="5"/>
-      <c r="F4" s="5"/>
-      <c r="G4" s="5"/>
-      <c r="H4" s="5"/>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A5" s="5"/>
-      <c r="B5" s="5"/>
-      <c r="C5" s="5"/>
-      <c r="D5" s="5"/>
-      <c r="E5" s="5"/>
-      <c r="F5" s="5"/>
-      <c r="G5" s="5"/>
-      <c r="H5" s="5"/>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A6" s="5"/>
-      <c r="B6" s="5"/>
-      <c r="C6" s="5"/>
-      <c r="D6" s="5"/>
-      <c r="E6" s="5"/>
-      <c r="F6" s="5"/>
-      <c r="G6" s="5"/>
-      <c r="H6" s="5"/>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A7" s="5"/>
-      <c r="B7" s="5"/>
-      <c r="C7" s="5"/>
-      <c r="D7" s="5"/>
-      <c r="E7" s="5"/>
-      <c r="F7" s="5"/>
-      <c r="G7" s="5"/>
-      <c r="H7" s="5"/>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A8" s="5"/>
-      <c r="B8" s="5"/>
-      <c r="C8" s="5"/>
-      <c r="D8" s="5"/>
-      <c r="E8" s="5"/>
-      <c r="F8" s="5"/>
-      <c r="G8" s="5"/>
-      <c r="H8" s="5"/>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A9" s="5"/>
-      <c r="B9" s="5"/>
-      <c r="C9" s="5"/>
-      <c r="D9" s="5"/>
-      <c r="E9" s="5"/>
-      <c r="F9" s="5"/>
-      <c r="G9" s="5"/>
-      <c r="H9" s="5"/>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A10" s="5"/>
-      <c r="B10" s="5"/>
-      <c r="C10" s="5"/>
-      <c r="D10" s="5"/>
-      <c r="E10" s="5"/>
-      <c r="F10" s="5"/>
-      <c r="G10" s="5"/>
-      <c r="H10" s="5"/>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A11" s="5"/>
-      <c r="B11" s="5"/>
-      <c r="C11" s="5"/>
-      <c r="D11" s="5"/>
-      <c r="E11" s="5"/>
-      <c r="F11" s="5"/>
-      <c r="G11" s="5"/>
-      <c r="H11" s="5"/>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A12" s="5"/>
-      <c r="B12" s="5"/>
-      <c r="C12" s="5"/>
-      <c r="D12" s="5"/>
-      <c r="E12" s="5"/>
-      <c r="F12" s="5"/>
-      <c r="G12" s="5"/>
-      <c r="H12" s="5"/>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A13" s="5"/>
-      <c r="B13" s="5"/>
-      <c r="C13" s="5"/>
-      <c r="D13" s="5"/>
-      <c r="E13" s="5"/>
-      <c r="F13" s="5"/>
-      <c r="G13" s="5"/>
-      <c r="H13" s="5"/>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A14" s="5"/>
-      <c r="B14" s="5"/>
-      <c r="C14" s="5"/>
-      <c r="D14" s="5"/>
-      <c r="E14" s="5"/>
-      <c r="F14" s="5"/>
-      <c r="G14" s="5"/>
-      <c r="H14" s="5"/>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A15" s="5"/>
-      <c r="B15" s="5"/>
-      <c r="C15" s="5"/>
-      <c r="D15" s="5"/>
-      <c r="E15" s="5"/>
-      <c r="F15" s="5"/>
-      <c r="G15" s="5"/>
-      <c r="H15" s="5"/>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A16" s="5"/>
-      <c r="B16" s="5"/>
-      <c r="C16" s="5"/>
-      <c r="D16" s="5"/>
-      <c r="E16" s="5"/>
-      <c r="F16" s="5"/>
-      <c r="G16" s="5"/>
-      <c r="H16" s="5"/>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A17" s="5"/>
-      <c r="B17" s="5"/>
-      <c r="C17" s="5"/>
-      <c r="D17" s="5"/>
-      <c r="E17" s="5"/>
-      <c r="F17" s="5"/>
-      <c r="G17" s="5"/>
-      <c r="H17" s="5"/>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A18" s="5"/>
-      <c r="B18" s="5"/>
-      <c r="C18" s="5"/>
-      <c r="D18" s="5"/>
-      <c r="E18" s="5"/>
-      <c r="F18" s="5"/>
-      <c r="G18" s="5"/>
-      <c r="H18" s="5"/>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A19" s="5"/>
-      <c r="B19" s="5"/>
-      <c r="C19" s="5"/>
-      <c r="D19" s="5"/>
-      <c r="E19" s="5"/>
-      <c r="F19" s="5"/>
-      <c r="G19" s="5"/>
-      <c r="H19" s="5"/>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A20" s="5"/>
-      <c r="B20" s="5"/>
-      <c r="C20" s="5"/>
-      <c r="D20" s="5"/>
-      <c r="E20" s="5"/>
-      <c r="F20" s="5"/>
-      <c r="G20" s="5"/>
-      <c r="H20" s="5"/>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A21" s="5"/>
-      <c r="B21" s="5"/>
-      <c r="C21" s="5"/>
-      <c r="D21" s="5"/>
-      <c r="E21" s="5"/>
-      <c r="F21" s="5"/>
-      <c r="G21" s="5"/>
-      <c r="H21" s="5"/>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A22" s="5"/>
-      <c r="B22" s="5"/>
-      <c r="C22" s="5"/>
-      <c r="D22" s="5"/>
-      <c r="E22" s="5"/>
-      <c r="F22" s="5"/>
-      <c r="G22" s="5"/>
-      <c r="H22" s="5"/>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A23" s="5"/>
-      <c r="B23" s="5"/>
-      <c r="C23" s="5"/>
-      <c r="D23" s="5"/>
-      <c r="E23" s="5"/>
-      <c r="F23" s="5"/>
-      <c r="G23" s="5"/>
-      <c r="H23" s="5"/>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A24" s="5"/>
-      <c r="B24" s="5"/>
-      <c r="C24" s="5"/>
-      <c r="D24" s="5"/>
-      <c r="E24" s="5"/>
-      <c r="F24" s="5"/>
-      <c r="G24" s="5"/>
-      <c r="H24" s="5"/>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A25" s="5"/>
-      <c r="B25" s="5"/>
-      <c r="C25" s="5"/>
-      <c r="D25" s="5"/>
-      <c r="E25" s="5"/>
-      <c r="F25" s="5"/>
-      <c r="G25" s="5"/>
-      <c r="H25" s="5"/>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A26" s="5"/>
-      <c r="B26" s="5"/>
-      <c r="C26" s="5"/>
-      <c r="D26" s="5"/>
-      <c r="E26" s="5"/>
-      <c r="F26" s="5"/>
-      <c r="G26" s="5"/>
-      <c r="H26" s="5"/>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A27" s="5"/>
-      <c r="B27" s="5"/>
-      <c r="C27" s="5"/>
-      <c r="D27" s="5"/>
-      <c r="E27" s="5"/>
-      <c r="F27" s="5"/>
-      <c r="G27" s="5"/>
-      <c r="H27" s="5"/>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A28" s="5"/>
-      <c r="B28" s="5"/>
-      <c r="C28" s="5"/>
-      <c r="D28" s="5"/>
-      <c r="E28" s="5"/>
-      <c r="F28" s="5"/>
-      <c r="G28" s="5"/>
-      <c r="H28" s="5"/>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A29" s="5"/>
-      <c r="B29" s="5"/>
-      <c r="C29" s="5"/>
-      <c r="D29" s="5"/>
-      <c r="E29" s="5"/>
-      <c r="F29" s="5"/>
-      <c r="G29" s="5"/>
-      <c r="H29" s="5"/>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A30" s="5"/>
-      <c r="B30" s="5"/>
-      <c r="C30" s="5"/>
-      <c r="D30" s="5"/>
-      <c r="E30" s="5"/>
-      <c r="F30" s="5"/>
-      <c r="G30" s="5"/>
-      <c r="H30" s="5"/>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A31" s="5"/>
-      <c r="B31" s="5"/>
-      <c r="C31" s="5"/>
-      <c r="D31" s="5"/>
-      <c r="E31" s="5"/>
-      <c r="F31" s="5"/>
-      <c r="G31" s="5"/>
-      <c r="H31" s="5"/>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>